--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>834.6420000000001</v>
+        <v>37130.21</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>212.818</v>
+        <v>9467.5</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15.72</v>
+        <v>699.33</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1750.812</v>
+        <v>77887.3</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>156.871</v>
+        <v>6978.62</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28.522</v>
+        <v>1268.84</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1009.19021</v>
+        <v>44895.23</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>497.448</v>
+        <v>22129.67</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>497.448</v>
+        <v>22129.67</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>177.714</v>
+        <v>7905.85</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>244.631</v>
+        <v>10882.75</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>159.065</v>
+        <v>7076.23</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>71.914</v>
+        <v>3199.19</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>823.847</v>
+        <v>36649.98</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26.068</v>
+        <v>1159.67</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>797.519</v>
+        <v>35478.74</v>
       </c>
     </row>
   </sheetData>
